--- a/AAII_Financials/Yearly/LKFN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LKFN_YR_FIN.xlsx
@@ -735,7 +735,7 @@
         <v>257200</v>
       </c>
       <c r="E8" s="3">
-        <v>236800</v>
+        <v>235800</v>
       </c>
       <c r="F8" s="3">
         <v>241000</v>
@@ -837,7 +837,7 @@
         <v>257200</v>
       </c>
       <c r="E10" s="3">
-        <v>236800</v>
+        <v>235800</v>
       </c>
       <c r="F10" s="3">
         <v>241000</v>
@@ -1011,7 +1011,7 @@
         <v>5</v>
       </c>
       <c r="E14" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="F14" s="3">
         <v>18100</v>
@@ -1182,7 +1182,7 @@
         <v>128900</v>
       </c>
       <c r="E18" s="3">
-        <v>119700</v>
+        <v>118700</v>
       </c>
       <c r="F18" s="3">
         <v>131800</v>
@@ -1305,7 +1305,7 @@
         <v>131600</v>
       </c>
       <c r="E21" s="3">
-        <v>122200</v>
+        <v>121200</v>
       </c>
       <c r="F21" s="3">
         <v>134600</v>
